--- a/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -828,7 +828,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)</t>
+Reference(Group|4.0.1)</t>
   </si>
   <si>
     <t>Type of individual the activity definition is intended for</t>
@@ -846,7 +846,7 @@
     <t>The possible types of subjects for an activity (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.0.1</t>
   </si>
   <si>
     <t>Definition.subject</t>
@@ -1226,7 +1226,7 @@
     <t>ActivityDefinition.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1440,7 +1440,7 @@
     <t>Defines roles played by participants for the action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/action-participant-role|4.0.1</t>
   </si>
   <si>
     <t>.role.code</t>
@@ -1449,7 +1449,7 @@
     <t>ActivityDefinition.product[x]</t>
   </si>
   <si>
-    <t>Reference(Medication|Substance)
+    <t>Reference(Medication|4.0.1|Substance|4.0.1)
 CodeableConcept</t>
   </si>
   <si>
@@ -1462,7 +1462,7 @@
     <t>Code describing the type of substance or medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>.participation[typeCode=CSM].role</t>
@@ -1475,7 +1475,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1525,7 +1525,7 @@
     <t>A code that identifies the anatomical location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>.targetSiteCode {for classCode=PROC, SBADM}</t>
@@ -1534,7 +1534,7 @@
     <t>ActivityDefinition.specimenRequirement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(SpecimenDefinition)
+    <t xml:space="preserve">Reference(SpecimenDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1550,7 +1550,7 @@
     <t>ActivityDefinition.observationRequirement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ObservationDefinition)
+    <t xml:space="preserve">Reference(ObservationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1575,7 +1575,7 @@
     <t>ActivityDefinition.transform</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureMap)
+    <t xml:space="preserve">canonical(StructureMap|4.0.1)
 </t>
   </si>
   <si>

--- a/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2838" uniqueCount="521">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1483,6 +1483,10 @@
   </si>
   <si>
     <t>Identifies the quantity expected to be consumed at once (per dose, per meal, etc.).</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.quantity {for classCode=SPLY}</t>
@@ -9475,13 +9479,13 @@
         <v>75</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>96</v>
+        <v>471</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>75</v>
@@ -9492,10 +9496,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9518,16 +9522,16 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9577,7 +9581,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -9595,7 +9599,7 @@
         <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>75</v>
@@ -9606,10 +9610,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9635,16 +9639,16 @@
         <v>306</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
@@ -9672,10 +9676,10 @@
         <v>455</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>75</v>
@@ -9693,7 +9697,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -9711,7 +9715,7 @@
         <v>75</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>75</v>
@@ -9722,10 +9726,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9748,17 +9752,17 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -9807,7 +9811,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -9836,10 +9840,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9862,17 +9866,17 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>75</v>
@@ -9921,7 +9925,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -9950,10 +9954,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9976,13 +9980,13 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10033,7 +10037,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10062,10 +10066,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10088,16 +10092,16 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10147,7 +10151,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10176,10 +10180,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10205,13 +10209,13 @@
         <v>428</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10261,7 +10265,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10290,10 +10294,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10402,10 +10406,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10516,10 +10520,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10632,10 +10636,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10661,13 +10665,13 @@
         <v>219</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10717,7 +10721,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>84</v>
@@ -10746,10 +10750,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10772,16 +10776,16 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10831,7 +10835,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>84</v>

--- a/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
+++ b/fhir/StructureDefinition-ehealth-activitydefinition.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
